--- a/材料属性列表_新批注已应用.xlsx
+++ b/材料属性列表_新批注已应用.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1221">
   <si>
     <t>短ID</t>
   </si>
@@ -190,6 +190,9 @@
     <t>Warden Tendril</t>
   </si>
   <si>
+    <t>是有机物，不是金属</t>
+  </si>
+  <si>
     <t>compressed_solidified_flux_experience</t>
   </si>
   <si>
@@ -199,6 +202,9 @@
     <t>Compressed Solidified Flux Experience</t>
   </si>
   <si>
+    <t>是宝石，不是金属</t>
+  </si>
+  <si>
     <t>blaze_cube</t>
   </si>
   <si>
@@ -208,6 +214,9 @@
     <t>Blaze Cube</t>
   </si>
   <si>
+    <t>稀有宝石，增强10倍</t>
+  </si>
+  <si>
     <t>crystal_matrix_ingot</t>
   </si>
   <si>
@@ -217,6 +226,9 @@
     <t>Crystal Matrix Ingot</t>
   </si>
   <si>
+    <t>稀有金属，增强10倍</t>
+  </si>
+  <si>
     <t>endest_pearl</t>
   </si>
   <si>
@@ -226,6 +238,9 @@
     <t>Endest Pearl</t>
   </si>
   <si>
+    <t>稀有宝石，增强5倍</t>
+  </si>
+  <si>
     <t>infinity_ingot</t>
   </si>
   <si>
@@ -271,6 +286,9 @@
     <t>Quark Ingot</t>
   </si>
   <si>
+    <t>终极金属，增加至护甲值1000，其它属性相应增加</t>
+  </si>
+  <si>
     <t>egg</t>
   </si>
   <si>
@@ -472,6 +490,9 @@
     <t>Null Block</t>
   </si>
   <si>
+    <t>石头</t>
+  </si>
+  <si>
     <t>null_end_stone</t>
   </si>
   <si>
@@ -490,6 +511,9 @@
     <t>Null Leaves</t>
   </si>
   <si>
+    <t>有机物</t>
+  </si>
+  <si>
     <t>orange_maple</t>
   </si>
   <si>
@@ -724,6 +748,9 @@
     <t>Lacrima</t>
   </si>
   <si>
+    <t>宝石，增强2倍</t>
+  </si>
+  <si>
     <t>void</t>
   </si>
   <si>
@@ -742,6 +769,9 @@
     <t>Void Stone</t>
   </si>
   <si>
+    <t>削弱50%</t>
+  </si>
+  <si>
     <t>witherite_ingot</t>
   </si>
   <si>
@@ -769,6 +799,9 @@
     <t>Honey</t>
   </si>
   <si>
+    <t>删除</t>
+  </si>
+  <si>
     <t>limestone</t>
   </si>
   <si>
@@ -841,6 +874,9 @@
     <t>Honey Butter</t>
   </si>
   <si>
+    <t>是覆层</t>
+  </si>
+  <si>
     <t>super_butter</t>
   </si>
   <si>
@@ -940,6 +976,9 @@
     <t>Alloy Creative</t>
   </si>
   <si>
+    <t>mek的合金等级：灌注&lt;强化&lt;原子&lt;超频&lt;绝对&lt;亚原子&lt;热核&lt;奇点&lt;闪耀&lt;超界&lt;光谱，亚原子及以上为稀有金属，最高光谱属性约为护甲值200，其它按比例缩放</t>
+  </si>
+  <si>
     <t>alloy_exoversal</t>
   </si>
   <si>
@@ -1039,6 +1078,9 @@
     <t>Crystaltine Ingot</t>
   </si>
   <si>
+    <t>金属</t>
+  </si>
+  <si>
     <t>ender_ingot</t>
   </si>
   <si>
@@ -1093,6 +1135,9 @@
     <t>Canvas</t>
   </si>
   <si>
+    <t>有机物，削弱75%</t>
+  </si>
+  <si>
     <t>straw</t>
   </si>
   <si>
@@ -1693,6 +1738,9 @@
     <t>Cosmic Gold Ingot</t>
   </si>
   <si>
+    <t>稀有金属，增强6倍</t>
+  </si>
+  <si>
     <t>demonite_ingot</t>
   </si>
   <si>
@@ -1837,6 +1885,9 @@
     <t>Solar Core</t>
   </si>
   <si>
+    <t>宝石，削弱30%</t>
+  </si>
+  <si>
     <t>spider_fang</t>
   </si>
   <si>
@@ -1909,6 +1960,9 @@
     <t>Blazum Ingot</t>
   </si>
   <si>
+    <t>覆层</t>
+  </si>
+  <si>
     <t>derium_ingot</t>
   </si>
   <si>
@@ -2098,6 +2152,9 @@
     <t>Red Shaft</t>
   </si>
   <si>
+    <t>手柄</t>
+  </si>
+  <si>
     <t>red_string</t>
   </si>
   <si>
@@ -2107,6 +2164,9 @@
     <t>Red String</t>
   </si>
   <si>
+    <t>线，有机物</t>
+  </si>
+  <si>
     <t>pork</t>
   </si>
   <si>
@@ -2188,6 +2248,9 @@
     <t>Fluorite</t>
   </si>
   <si>
+    <t>用alltheores的</t>
+  </si>
+  <si>
     <t>hdpe_stick</t>
   </si>
   <si>
@@ -2206,6 +2269,9 @@
     <t>Pellet Antimatter</t>
   </si>
   <si>
+    <t>宝石</t>
+  </si>
+  <si>
     <t>pellet_plutonium</t>
   </si>
   <si>
@@ -2233,6 +2299,9 @@
     <t>Substrate</t>
   </si>
   <si>
+    <t>削弱75%</t>
+  </si>
+  <si>
     <t>alloy_radiance</t>
   </si>
   <si>
@@ -2287,6 +2356,9 @@
     <t>Empty Crystal</t>
   </si>
   <si>
+    <t>削弱30%</t>
+  </si>
+  <si>
     <t>scrap_box</t>
   </si>
   <si>
@@ -2296,6 +2368,9 @@
     <t>Scrap Box</t>
   </si>
   <si>
+    <t>增强50%</t>
+  </si>
+  <si>
     <t>uu_matter</t>
   </si>
   <si>
@@ -2710,6 +2785,9 @@
     <t>Aether Vestiges</t>
   </si>
   <si>
+    <t>稀有宝石，增强4倍</t>
+  </si>
+  <si>
     <t>aloe</t>
   </si>
   <si>
@@ -2728,6 +2806,9 @@
     <t>Bedrock Dust</t>
   </si>
   <si>
+    <t>稀有石头，增强1.5倍</t>
+  </si>
+  <si>
     <t>bismuth_crystal</t>
   </si>
   <si>
@@ -2737,6 +2818,9 @@
     <t>Bismuth Crystal</t>
   </si>
   <si>
+    <t>稀有宝石，增强2倍</t>
+  </si>
+  <si>
     <t>blazing</t>
   </si>
   <si>
@@ -2782,6 +2866,9 @@
     <t>Downstone Fragments</t>
   </si>
   <si>
+    <t>稀有宝石，增强1.5倍</t>
+  </si>
+  <si>
     <t>dragonbone_chunk</t>
   </si>
   <si>
@@ -3313,6 +3400,9 @@
     <t>Air Shard</t>
   </si>
   <si>
+    <t>和同模组的火之碎片数值相同，碎片都是宝石</t>
+  </si>
+  <si>
     <t>ancient_stone</t>
   </si>
   <si>
@@ -3466,6 +3556,9 @@
     <t>Ichor</t>
   </si>
   <si>
+    <t>稀有覆层，增强10倍</t>
+  </si>
+  <si>
     <t>ichorcloth</t>
   </si>
   <si>
@@ -3475,6 +3568,9 @@
     <t>Ichorcloth</t>
   </si>
   <si>
+    <t>稀有有机物，增强10倍</t>
+  </si>
+  <si>
     <t>ichorium_ingot</t>
   </si>
   <si>
@@ -3599,6 +3695,9 @@
   </si>
   <si>
     <t>Crystalline</t>
+  </si>
+  <si>
+    <t>只有宝石能做顶端升级；被统一的物品原来的也要加入材料列表（仅限不同颜色的同一种物品，或者类似的物品，像铁锭和铁块就只要铁锭）</t>
   </si>
 </sst>
 </file>
@@ -4591,7 +4690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G395"/>
+  <dimension ref="A1:G396"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4935,17 +5034,19 @@
       <c r="F16" s="2">
         <v>8.97</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>21.496</v>
@@ -4956,17 +5057,19 @@
       <c r="F17" s="2">
         <v>5.352</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2">
         <v>13.34</v>
@@ -4977,17 +5080,19 @@
       <c r="F18" s="2">
         <v>3.471</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2">
         <v>25.529</v>
@@ -4998,17 +5103,19 @@
       <c r="F19" s="2">
         <v>7.581</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2">
         <v>25.529</v>
@@ -5019,17 +5126,19 @@
       <c r="F20" s="2">
         <v>7.581</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2">
         <v>510.504</v>
@@ -5044,13 +5153,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D22" s="2">
         <v>276.3</v>
@@ -5065,13 +5174,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2">
         <v>11.753</v>
@@ -5082,17 +5191,19 @@
       <c r="F23" s="2">
         <v>2.98</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D24" s="2">
         <v>151.299</v>
@@ -5105,15 +5216,15 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" ht="27" spans="1:7">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2">
         <v>300</v>
@@ -5124,59 +5235,61 @@
       <c r="F25" s="2">
         <v>100</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2">
         <v>4.929</v>
@@ -5191,13 +5304,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D29" s="2">
         <v>12.412</v>
@@ -5208,17 +5321,19 @@
       <c r="F29" s="2">
         <v>3.182</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2">
         <v>4.831</v>
@@ -5233,34 +5348,34 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D32" s="2">
         <v>11.61</v>
@@ -5271,38 +5386,40 @@
       <c r="F32" s="2">
         <v>2.936</v>
       </c>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D34" s="2">
         <v>2.257</v>
@@ -5317,13 +5434,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D35" s="2">
         <v>3.562</v>
@@ -5338,13 +5455,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D36" s="2">
         <v>3.406</v>
@@ -5359,97 +5476,97 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G39" s="3"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G40" s="3"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D41" s="2">
         <v>3.093</v>
@@ -5464,13 +5581,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D42" s="2">
         <v>3.286</v>
@@ -5485,13 +5602,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2">
         <v>5.402</v>
@@ -5506,13 +5623,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D44" s="2">
         <v>3.64</v>
@@ -5527,13 +5644,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D45" s="2">
         <v>3.404</v>
@@ -5548,13 +5665,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D46" s="2">
         <v>5.116</v>
@@ -5569,13 +5686,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D47" s="2">
         <v>12.262</v>
@@ -5586,17 +5703,19 @@
       <c r="F47" s="2">
         <v>3.136</v>
       </c>
-      <c r="G47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D48" s="2">
         <v>10.927</v>
@@ -5607,17 +5726,19 @@
       <c r="F48" s="2">
         <v>2.73</v>
       </c>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B49" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D49" s="2">
         <v>12.962</v>
@@ -5628,38 +5749,40 @@
       <c r="F49" s="2">
         <v>3.353</v>
       </c>
-      <c r="G49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D50" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F50" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G50" s="3"/>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D51" s="2">
         <v>4.536</v>
@@ -5674,34 +5797,34 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G52" s="3"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D53" s="2">
         <v>3.562</v>
@@ -5716,13 +5839,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D54" s="2">
         <v>3.746</v>
@@ -5737,139 +5860,139 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D55" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F55" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G55" s="3"/>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F56" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G56" s="3"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E57" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F57" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G57" s="3"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B58" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E58" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F58" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G58" s="3"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E59" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F59" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G59" s="3"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G60" s="3"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D61" s="2">
         <v>3.317</v>
@@ -5884,34 +6007,34 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C62" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E62" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F62" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G62" s="3"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B63" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D63" s="2">
         <v>4.766</v>
@@ -5926,13 +6049,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C64" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D64" s="2">
         <v>3.418</v>
@@ -5947,55 +6070,55 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E65" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F65" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G65" s="3"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B66" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C66" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F66" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G66" s="3"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C67" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D67" s="2">
         <v>17.582</v>
@@ -6010,13 +6133,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B68" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C68" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D68" s="2">
         <v>21.958</v>
@@ -6031,13 +6154,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C69" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D69" s="2">
         <v>3.225</v>
@@ -6052,34 +6175,34 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E70" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F70" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G70" s="3"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B71" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D71" s="2">
         <v>66.504</v>
@@ -6094,13 +6217,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C72" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D72" s="2">
         <v>12.242</v>
@@ -6115,13 +6238,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D73" s="2">
         <v>124.65</v>
@@ -6136,34 +6259,34 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C74" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E74" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F74" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G74" s="3"/>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B75" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C75" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D75" s="2">
         <v>11.037</v>
@@ -6174,17 +6297,19 @@
       <c r="F75" s="2">
         <v>2.763</v>
       </c>
-      <c r="G75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D76" s="2">
         <v>21.587</v>
@@ -6199,13 +6324,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C77" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D77" s="2">
         <v>20.015</v>
@@ -6216,17 +6341,19 @@
       <c r="F77" s="2">
         <v>6.083</v>
       </c>
-      <c r="G77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D78" s="2">
         <v>11.31</v>
@@ -6237,17 +6364,19 @@
       <c r="F78" s="2">
         <v>2.845</v>
       </c>
-      <c r="G78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B79" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D79" s="2">
         <v>12.367</v>
@@ -6262,34 +6391,36 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C80" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D80" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F80" t="s">
-        <v>81</v>
-      </c>
-      <c r="G80" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B81" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C81" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D81" s="2">
         <v>5.14</v>
@@ -6304,13 +6435,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B82" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D82" s="2">
         <v>19.584</v>
@@ -6325,34 +6456,36 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C83" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E83" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F83" t="s">
-        <v>81</v>
-      </c>
-      <c r="G83" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C84" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D84" s="2">
         <v>4.805</v>
@@ -6367,13 +6500,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B85" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C85" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="D85" s="2">
         <v>25.529</v>
@@ -6388,13 +6521,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D86" s="2">
         <v>12.017</v>
@@ -6409,13 +6542,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B87" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C87" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D87" s="2">
         <v>16.5</v>
@@ -6430,55 +6563,59 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B88" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E88" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>81</v>
-      </c>
-      <c r="G88" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E89" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
-      </c>
-      <c r="G89" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B90" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C90" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D90" s="2">
         <v>11.959</v>
@@ -6493,55 +6630,57 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B91" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E91" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F91" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G91" s="3"/>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C92" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E92" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F92" t="s">
-        <v>81</v>
-      </c>
-      <c r="G92" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B93" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C93" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D93" s="2">
         <v>45</v>
@@ -6556,13 +6695,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C94" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="D94" s="2">
         <v>3.705</v>
@@ -6577,13 +6716,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B95" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C95" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="D95" s="2">
         <v>5.058</v>
@@ -6598,13 +6737,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B96" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C96" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D96" s="2">
         <v>4.411</v>
@@ -6619,13 +6758,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B97" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C97" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D97" s="2">
         <v>4.317</v>
@@ -6640,13 +6779,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B98" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D98" s="2">
         <v>4.612</v>
@@ -6659,15 +6798,15 @@
       </c>
       <c r="G98" s="3"/>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" ht="54" spans="1:7">
       <c r="A99" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B99" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C99" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="D99" s="2">
         <v>195.059</v>
@@ -6678,17 +6817,19 @@
       <c r="F99" s="2">
         <v>65.02</v>
       </c>
-      <c r="G99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B100" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C100" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D100" s="2">
         <v>97.766</v>
@@ -6703,13 +6844,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B101" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C101" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D101" s="2">
         <v>11.225</v>
@@ -6724,13 +6865,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B102" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C102" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D102" s="2">
         <v>204.584</v>
@@ -6745,13 +6886,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B103" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C103" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D103" s="2">
         <v>13.304</v>
@@ -6766,13 +6907,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B104" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C104" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D104" s="2">
         <v>50.916</v>
@@ -6787,13 +6928,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C105" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D105" s="2">
         <v>94.464</v>
@@ -6808,13 +6949,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C106" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D106" s="2">
         <v>36.363</v>
@@ -6825,17 +6966,19 @@
       <c r="F106" s="2">
         <v>9.276</v>
       </c>
-      <c r="G106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C107" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="D107" s="2">
         <v>14.188</v>
@@ -6850,13 +6993,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B108" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C108" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D108" s="2">
         <v>21.908</v>
@@ -6871,13 +7014,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C109" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="D109" s="2">
         <v>16.771</v>
@@ -6892,13 +7035,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C110" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D110" s="2">
         <v>46.492</v>
@@ -6909,17 +7052,19 @@
       <c r="F110" s="2">
         <v>11.76</v>
       </c>
-      <c r="G110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B111" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C111" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D111" s="2">
         <v>9.854</v>
@@ -6934,13 +7079,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B112" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D112" s="2">
         <v>27.37</v>
@@ -6955,13 +7100,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B113" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C113" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D113" s="2">
         <v>10.714</v>
@@ -6976,13 +7121,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B114" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="D114" s="2">
         <v>11.209</v>
@@ -6997,13 +7142,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C115" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D115" s="2">
         <v>500.885</v>
@@ -7018,13 +7163,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B116" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C116" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="D116" s="2">
         <v>12.389</v>
@@ -7035,80 +7180,82 @@
       <c r="F116" s="2">
         <v>3.175</v>
       </c>
-      <c r="G116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B117" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C117" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="D117" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E117" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F117" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G117" s="3"/>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C118" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E118" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F118" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G118" s="3"/>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B119" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C119" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="D119" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E119" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F119" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G119" s="3"/>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B120" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="C120" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="D120" s="2">
         <v>3.748</v>
@@ -7123,475 +7270,475 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B121" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C121" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="D121" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E121" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F121" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G121" s="3"/>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B122" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="C122" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="D122" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E122" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F122" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G122" s="3"/>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="B123" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C123" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="D123" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E123" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F123" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G123" s="3"/>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B124" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C124" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="D124" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E124" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F124" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G124" s="3"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="B125" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C125" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="D125" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E125" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F125" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G125" s="3"/>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C126" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D126" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E126" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F126" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G126" s="3"/>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B127" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C127" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="D127" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E127" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F127" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G127" s="3"/>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B128" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C128" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="D128" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E128" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F128" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G128" s="3"/>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B129" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="C129" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D129" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E129" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F129" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G129" s="3"/>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="B130" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C130" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D130" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E130" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F130" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G130" s="3"/>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="B131" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="C131" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E131" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F131" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G131" s="3"/>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B132" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C132" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E132" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F132" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G132" s="3"/>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="B133" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="C133" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="D133" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E133" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F133" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G133" s="3"/>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="B134" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C134" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D134" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E134" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F134" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G134" s="3"/>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="B135" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C135" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="D135" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E135" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F135" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G135" s="3"/>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="C136" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="D136" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E136" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F136" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G136" s="3"/>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="B137" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C137" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="D137" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E137" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F137" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G137" s="3"/>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="B138" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C138" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="D138" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E138" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F138" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G138" s="3"/>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B139" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C139" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="D139" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E139" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F139" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G139" s="3"/>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B140" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C140" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="D140" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E140" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F140" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G140" s="3"/>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B141" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C141" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D141" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E141" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F141" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G141" s="3"/>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B142" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C142" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D142" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E142" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F142" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G142" s="3"/>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B143" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C143" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="D143" s="2">
         <v>3.2</v>
@@ -7606,160 +7753,160 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B144" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C144" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="D144" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E144" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F144" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G144" s="3"/>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B145" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C145" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="D145" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E145" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F145" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G145" s="3"/>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B146" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D146" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E146" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F146" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G146" s="3"/>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="B147" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C147" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="D147" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E147" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F147" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G147" s="3"/>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="B148" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="D148" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E148" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F148" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G148" s="3"/>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B149" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="C149" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="D149" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E149" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F149" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G149" s="3"/>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="B150" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C150" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="D150" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E150" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F150" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G150" s="3"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="B151" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="D151" s="2">
         <v>6.744</v>
@@ -7774,13 +7921,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B152" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="C152" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="D152" s="2">
         <v>3.419</v>
@@ -7795,76 +7942,76 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="B153" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C153" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="D153" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E153" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F153" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G153" s="3"/>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="B154" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C154" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E154" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F154" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G154" s="3"/>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="B155" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="C155" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D155" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E155" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F155" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G155" s="3"/>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="B156" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C156" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="D156" s="2">
         <v>3.206</v>
@@ -7879,160 +8026,160 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="B157" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C157" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="D157" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E157" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F157" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G157" s="3"/>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="B158" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="C158" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="D158" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E158" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F158" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G158" s="3"/>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B159" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C159" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="D159" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E159" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F159" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G159" s="3"/>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B160" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C160" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D160" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E160" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F160" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G160" s="3"/>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B161" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="C161" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D161" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E161" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F161" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G161" s="3"/>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="B162" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C162" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D162" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E162" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F162" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G162" s="3"/>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B163" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C163" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="D163" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E163" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F163" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G163" s="3"/>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="B164" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="C164" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="D164" s="2">
         <v>3.505</v>
@@ -8047,76 +8194,76 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="B165" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C165" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="D165" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E165" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F165" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G165" s="3"/>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="B166" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C166" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="D166" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E166" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F166" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G166" s="3"/>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="B167" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="C167" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="D167" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E167" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F167" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G167" s="3"/>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="B168" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C168" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="D168" s="2">
         <v>29.973</v>
@@ -8131,13 +8278,13 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="B169" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="C169" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="D169" s="2">
         <v>29.973</v>
@@ -8152,13 +8299,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="B170" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="C170" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="D170" s="2">
         <v>29.973</v>
@@ -8173,13 +8320,13 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="B171" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="C171" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="D171" s="2">
         <v>19.928</v>
@@ -8194,13 +8341,13 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="B172" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="C172" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="D172" s="2">
         <v>29.973</v>
@@ -8215,13 +8362,13 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="B173" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="C173" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="D173" s="2">
         <v>35.967</v>
@@ -8236,13 +8383,13 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B174" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="C174" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="D174" s="2">
         <v>29.973</v>
@@ -8257,13 +8404,13 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="B175" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="C175" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="D175" s="2">
         <v>14.545</v>
@@ -8278,13 +8425,13 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="B176" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="C176" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="D176" s="2">
         <v>10.115</v>
@@ -8299,13 +8446,13 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="B177" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C177" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="D177" s="2">
         <v>13.289</v>
@@ -8320,13 +8467,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="B178" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="C178" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="D178" s="2">
         <v>29.973</v>
@@ -8341,55 +8488,55 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="B179" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="C179" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E179" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F179" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G179" s="3"/>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="B180" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C180" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="D180" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E180" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F180" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G180" s="3"/>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="B181" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="C181" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="D181" s="2">
         <v>25.263</v>
@@ -8404,34 +8551,34 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="B182" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="C182" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="D182" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E182" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F182" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G182" s="3"/>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="B183" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C183" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="D183" s="2">
         <v>12.876</v>
@@ -8442,17 +8589,19 @@
       <c r="F183" s="2">
         <v>3.326</v>
       </c>
-      <c r="G183" s="3"/>
+      <c r="G183" s="3" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B184" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="C184" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="D184" s="2">
         <v>25.46</v>
@@ -8467,13 +8616,13 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="B185" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="C185" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="D185" s="2">
         <v>115.668</v>
@@ -8484,17 +8633,19 @@
       <c r="F185" s="2">
         <v>38.556</v>
       </c>
-      <c r="G185" s="3"/>
+      <c r="G185" s="3" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="B186" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="C186" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="D186" s="2">
         <v>22.702</v>
@@ -8509,34 +8660,34 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="B187" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="C187" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="D187" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E187" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F187" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G187" s="3"/>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="B188" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="C188" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="D188" s="2">
         <v>11.426</v>
@@ -8547,17 +8698,19 @@
       <c r="F188" s="2">
         <v>2.88</v>
       </c>
-      <c r="G188" s="3"/>
+      <c r="G188" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="B189" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="C189" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="D189" s="2">
         <v>3.54</v>
@@ -8572,34 +8725,34 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="B190" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="C190" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E190" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F190" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G190" s="3"/>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="B191" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="C191" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="D191" s="2">
         <v>26.402</v>
@@ -8614,13 +8767,13 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="B192" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="C192" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="D192" s="2">
         <v>12.224</v>
@@ -8635,34 +8788,34 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="B193" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="C193" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E193" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F193" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G193" s="3"/>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B194" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="C194" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="D194" s="2">
         <v>12.014</v>
@@ -8677,13 +8830,13 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B195" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="C195" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="D195" s="2">
         <v>12.363</v>
@@ -8698,13 +8851,13 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="B196" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="C196" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="D196" s="2">
         <v>11.189</v>
@@ -8719,13 +8872,13 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="B197" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="C197" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D197" s="2">
         <v>12.572</v>
@@ -8740,13 +8893,13 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B198" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="C198" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="D198" s="2">
         <v>11.515</v>
@@ -8761,13 +8914,13 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="B199" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="C199" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="D199" s="2">
         <v>25.186</v>
@@ -8778,38 +8931,40 @@
       <c r="F199" s="2">
         <v>7.459</v>
       </c>
-      <c r="G199" s="3"/>
+      <c r="G199" s="3" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="B200" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="C200" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="D200" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E200" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F200" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G200" s="3"/>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="B201" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="C201" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="D201" s="2">
         <v>5.047</v>
@@ -8824,34 +8979,34 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="B202" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="C202" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="D202" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E202" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F202" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G202" s="3"/>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="B203" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="C203" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="D203" s="2">
         <v>13.39</v>
@@ -8866,13 +9021,13 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="B204" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="C204" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="D204" s="2">
         <v>3.562</v>
@@ -8887,13 +9042,13 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="B205" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="C205" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="D205" s="2">
         <v>49.383</v>
@@ -8908,13 +9063,13 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="B206" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="C206" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="D206" s="2">
         <v>14.541</v>
@@ -8929,13 +9084,13 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="B207" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="C207" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="D207" s="2">
         <v>22.312</v>
@@ -8946,17 +9101,19 @@
       <c r="F207" s="2">
         <v>5.598</v>
       </c>
-      <c r="G207" s="3"/>
+      <c r="G207" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="B208" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="C208" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="D208" s="2">
         <v>23.284</v>
@@ -8967,17 +9124,19 @@
       <c r="F208" s="2">
         <v>5.892</v>
       </c>
-      <c r="G208" s="3"/>
+      <c r="G208" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="B209" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="C209" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="D209" s="2">
         <v>23.636</v>
@@ -8988,17 +9147,19 @@
       <c r="F209" s="2">
         <v>6</v>
       </c>
-      <c r="G209" s="3"/>
+      <c r="G209" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="B210" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="C210" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="D210" s="2">
         <v>23.87</v>
@@ -9009,17 +9170,19 @@
       <c r="F210" s="2">
         <v>6.07</v>
       </c>
-      <c r="G210" s="3"/>
+      <c r="G210" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="B211" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="C211" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="D211" s="2">
         <v>21.338</v>
@@ -9034,97 +9197,97 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="B212" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="C212" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="D212" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E212" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F212" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G212" s="3"/>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="B213" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="C213" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E213" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F213" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G213" s="3"/>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="B214" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="C214" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
       <c r="D214" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E214" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F214" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G214" s="3"/>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="B215" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="C215" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E215" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F215" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G215" s="3"/>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="B216" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="C216" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="D216" s="2">
         <v>22.548</v>
@@ -9139,13 +9302,13 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="B217" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="C217" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="D217" s="2">
         <v>12.322</v>
@@ -9160,97 +9323,97 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="B218" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
       <c r="C218" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="D218" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E218" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F218" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G218" s="3"/>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="B219" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="C219" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E219" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F219" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G219" s="3"/>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="B220" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="C220" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="D220" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E220" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F220" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G220" s="3"/>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="B221" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C221" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="D221" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E221" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F221" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G221" s="3"/>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="B222" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="C222" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="D222" s="2">
         <v>26.653</v>
@@ -9265,34 +9428,34 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="B223" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C223" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="D223" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E223" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F223" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G223" s="3"/>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="B224" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="C224" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="D224" s="2">
         <v>34.689</v>
@@ -9307,13 +9470,13 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B225" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="C225" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="D225" s="2">
         <v>122.68</v>
@@ -9328,13 +9491,13 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="B226" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C226" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="D226" s="2">
         <v>19.305</v>
@@ -9349,13 +9512,13 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="B227" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="C227" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="D227" s="2">
         <v>17.682</v>
@@ -9370,13 +9533,13 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="B228" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="C228" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="D228" s="2">
         <v>10.032</v>
@@ -9387,17 +9550,19 @@
       <c r="F228" s="2">
         <v>2.837</v>
       </c>
-      <c r="G228" s="3"/>
+      <c r="G228" s="3" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="B229" t="s">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="C229" t="s">
-        <v>689</v>
+        <v>708</v>
       </c>
       <c r="D229" s="2">
         <v>9.136</v>
@@ -9408,101 +9573,103 @@
       <c r="F229" s="2">
         <v>2.534</v>
       </c>
-      <c r="G229" s="3"/>
+      <c r="G229" s="3" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="B230" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="C230" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="D230" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E230" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F230" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G230" s="3"/>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="B231" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="C231" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E231" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F231" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G231" s="3"/>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="B232" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="C232" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="D232" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E232" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F232" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G232" s="3"/>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="B233" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="C233" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E233" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F233" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G233" s="3"/>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="B234" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="C234" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="D234" s="2">
         <v>12.584</v>
@@ -9513,17 +9680,19 @@
       <c r="F234" s="2">
         <v>3.235</v>
       </c>
-      <c r="G234" s="3"/>
+      <c r="G234" s="3" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="B235" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="C235" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="D235" s="2">
         <v>12.764</v>
@@ -9538,13 +9707,13 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="B236" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="C236" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="D236" s="2">
         <v>12.647</v>
@@ -9559,13 +9728,13 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="B237" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="C237" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="D237" s="2">
         <v>10.724</v>
@@ -9580,13 +9749,13 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="B238" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="C238" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="D238" s="2">
         <v>10.833</v>
@@ -9597,17 +9766,19 @@
       <c r="F238" s="2">
         <v>2.701</v>
       </c>
-      <c r="G238" s="3"/>
+      <c r="G238" s="3" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="B239" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="C239" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="D239" s="2">
         <v>13.133</v>
@@ -9618,17 +9789,19 @@
       <c r="F239" s="2">
         <v>3.406</v>
       </c>
-      <c r="G239" s="3"/>
+      <c r="G239" s="3" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B240" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="C240" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D240" s="2">
         <v>81.766</v>
@@ -9639,17 +9812,19 @@
       <c r="F240" s="2">
         <v>27.255</v>
       </c>
-      <c r="G240" s="3"/>
+      <c r="G240" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>723</v>
+        <v>745</v>
       </c>
       <c r="B241" t="s">
-        <v>724</v>
+        <v>746</v>
       </c>
       <c r="C241" t="s">
-        <v>725</v>
+        <v>747</v>
       </c>
       <c r="D241" s="2">
         <v>45.112</v>
@@ -9664,13 +9839,13 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="B242" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
       <c r="C242" t="s">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="D242" s="2">
         <v>46.036</v>
@@ -9685,13 +9860,13 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="B243" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="C243" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="D243" s="2">
         <v>12.679</v>
@@ -9702,17 +9877,19 @@
       <c r="F243" s="2">
         <v>3.265</v>
       </c>
-      <c r="G243" s="3"/>
+      <c r="G243" s="3" t="s">
+        <v>754</v>
+      </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>732</v>
+        <v>755</v>
       </c>
       <c r="B244" t="s">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="C244" t="s">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="D244" s="2">
         <v>12.293</v>
@@ -9727,13 +9904,13 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>735</v>
+        <v>758</v>
       </c>
       <c r="B245" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="C245" t="s">
-        <v>737</v>
+        <v>760</v>
       </c>
       <c r="D245" s="2">
         <v>11.254</v>
@@ -9748,13 +9925,13 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="B246" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
       <c r="C246" t="s">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="D246" s="2">
         <v>12.603</v>
@@ -9769,13 +9946,13 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
       <c r="B247" t="s">
-        <v>742</v>
+        <v>765</v>
       </c>
       <c r="C247" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="D247" s="2">
         <v>11.496</v>
@@ -9790,13 +9967,13 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>744</v>
+        <v>767</v>
       </c>
       <c r="B248" t="s">
-        <v>745</v>
+        <v>768</v>
       </c>
       <c r="C248" t="s">
-        <v>746</v>
+        <v>769</v>
       </c>
       <c r="D248" s="2">
         <v>22.174</v>
@@ -9811,13 +9988,13 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>747</v>
+        <v>770</v>
       </c>
       <c r="B249" t="s">
-        <v>748</v>
+        <v>771</v>
       </c>
       <c r="C249" t="s">
-        <v>749</v>
+        <v>772</v>
       </c>
       <c r="D249" s="2">
         <v>11.135</v>
@@ -9828,17 +10005,19 @@
       <c r="F249" s="2">
         <v>2.792</v>
       </c>
-      <c r="G249" s="3"/>
+      <c r="G249" s="3" t="s">
+        <v>773</v>
+      </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>750</v>
+        <v>774</v>
       </c>
       <c r="B250" t="s">
-        <v>751</v>
+        <v>775</v>
       </c>
       <c r="C250" t="s">
-        <v>752</v>
+        <v>776</v>
       </c>
       <c r="D250" s="2">
         <v>12.418</v>
@@ -9849,17 +10028,19 @@
       <c r="F250" s="2">
         <v>3.184</v>
       </c>
-      <c r="G250" s="3"/>
+      <c r="G250" s="3" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="B251" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="C251" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="D251" s="2">
         <v>48.615</v>
@@ -9874,34 +10055,34 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="B252" t="s">
-        <v>757</v>
+        <v>782</v>
       </c>
       <c r="C252" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="D252" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E252" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F252" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G252" s="3"/>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="B253" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="C253" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="D253" s="2">
         <v>4.522</v>
@@ -9916,13 +10097,13 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="B254" t="s">
-        <v>763</v>
+        <v>788</v>
       </c>
       <c r="C254" t="s">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="D254" s="2">
         <v>28.95</v>
@@ -9937,13 +10118,13 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="B255" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="C255" t="s">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="D255" s="2">
         <v>8.566</v>
@@ -9958,13 +10139,13 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="B256" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
       <c r="C256" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="D256" s="2">
         <v>4.585</v>
@@ -9979,13 +10160,13 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="B257" t="s">
-        <v>772</v>
+        <v>797</v>
       </c>
       <c r="C257" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="D257" s="2">
         <v>32.184</v>
@@ -10000,13 +10181,13 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>774</v>
+        <v>799</v>
       </c>
       <c r="B258" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="C258" t="s">
-        <v>776</v>
+        <v>801</v>
       </c>
       <c r="D258" s="2">
         <v>9.89</v>
@@ -10021,76 +10202,76 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="B259" t="s">
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="C259" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E259" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F259" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G259" s="3"/>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>780</v>
+        <v>805</v>
       </c>
       <c r="B260" t="s">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="C260" t="s">
-        <v>782</v>
+        <v>807</v>
       </c>
       <c r="D260" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E260" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F260" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G260" s="3"/>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>783</v>
+        <v>808</v>
       </c>
       <c r="B261" t="s">
-        <v>784</v>
+        <v>809</v>
       </c>
       <c r="C261" t="s">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="D261" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E261" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F261" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G261" s="3"/>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>786</v>
+        <v>811</v>
       </c>
       <c r="B262" t="s">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="C262" t="s">
-        <v>788</v>
+        <v>813</v>
       </c>
       <c r="D262" s="2">
         <v>35.967</v>
@@ -10105,13 +10286,13 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>789</v>
+        <v>814</v>
       </c>
       <c r="B263" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="C263" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
       <c r="D263" s="2">
         <v>46.348</v>
@@ -10126,13 +10307,13 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>792</v>
+        <v>817</v>
       </c>
       <c r="B264" t="s">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="C264" t="s">
-        <v>794</v>
+        <v>819</v>
       </c>
       <c r="D264" s="2">
         <v>16.604</v>
@@ -10147,13 +10328,13 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="B265" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="C265" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="D265" s="2">
         <v>46.744</v>
@@ -10168,13 +10349,13 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="B266" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
       <c r="C266" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="D266" s="2">
         <v>21.075</v>
@@ -10189,13 +10370,13 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>801</v>
+        <v>826</v>
       </c>
       <c r="B267" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="C267" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="D267" s="2">
         <v>28.74</v>
@@ -10210,13 +10391,13 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="B268" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
       <c r="C268" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="D268" s="2">
         <v>49.472</v>
@@ -10231,13 +10412,13 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>807</v>
+        <v>832</v>
       </c>
       <c r="B269" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="C269" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="D269" s="2">
         <v>46.312</v>
@@ -10248,17 +10429,19 @@
       <c r="F269" s="2">
         <v>13.482</v>
       </c>
-      <c r="G269" s="3"/>
+      <c r="G269" s="3" t="s">
+        <v>773</v>
+      </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="B270" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="C270" t="s">
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="D270" s="2">
         <v>3.248</v>
@@ -10273,13 +10456,13 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="B271" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="C271" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="D271" s="2">
         <v>3.761</v>
@@ -10294,13 +10477,13 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="B272" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
       <c r="C272" t="s">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="D272" s="2">
         <v>22</v>
@@ -10315,34 +10498,34 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="B273" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="C273" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="D273" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E273" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F273" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G273" s="3"/>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="B274" t="s">
-        <v>823</v>
+        <v>848</v>
       </c>
       <c r="C274" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="D274" s="2">
         <v>13.41</v>
@@ -10357,34 +10540,34 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="B275" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="C275" t="s">
-        <v>827</v>
+        <v>852</v>
       </c>
       <c r="D275" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E275" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F275" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G275" s="3"/>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="B276" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="C276" t="s">
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="D276" s="2">
         <v>11.62</v>
@@ -10399,13 +10582,13 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>831</v>
+        <v>856</v>
       </c>
       <c r="B277" t="s">
-        <v>832</v>
+        <v>857</v>
       </c>
       <c r="C277" t="s">
-        <v>833</v>
+        <v>858</v>
       </c>
       <c r="D277" s="2">
         <v>4.472</v>
@@ -10420,13 +10603,13 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>834</v>
+        <v>859</v>
       </c>
       <c r="B278" t="s">
-        <v>835</v>
+        <v>860</v>
       </c>
       <c r="C278" t="s">
-        <v>836</v>
+        <v>861</v>
       </c>
       <c r="D278" s="2">
         <v>10.786</v>
@@ -10437,17 +10620,19 @@
       <c r="F278" s="2">
         <v>2.687</v>
       </c>
-      <c r="G278" s="3"/>
+      <c r="G278" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="B279" t="s">
-        <v>838</v>
+        <v>863</v>
       </c>
       <c r="C279" t="s">
-        <v>839</v>
+        <v>864</v>
       </c>
       <c r="D279" s="2">
         <v>4.998</v>
@@ -10462,13 +10647,13 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="B280" t="s">
-        <v>841</v>
+        <v>866</v>
       </c>
       <c r="C280" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="D280" s="2">
         <v>12.001</v>
@@ -10479,17 +10664,19 @@
       <c r="F280" s="2">
         <v>3.056</v>
       </c>
-      <c r="G280" s="3"/>
+      <c r="G280" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>843</v>
+        <v>868</v>
       </c>
       <c r="B281" t="s">
-        <v>844</v>
+        <v>869</v>
       </c>
       <c r="C281" t="s">
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="D281" s="2">
         <v>5.059</v>
@@ -10504,13 +10691,13 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>846</v>
+        <v>871</v>
       </c>
       <c r="B282" t="s">
-        <v>847</v>
+        <v>872</v>
       </c>
       <c r="C282" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="D282" s="2">
         <v>12.693</v>
@@ -10521,17 +10708,19 @@
       <c r="F282" s="2">
         <v>3.269</v>
       </c>
-      <c r="G282" s="3"/>
+      <c r="G282" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>849</v>
+        <v>874</v>
       </c>
       <c r="B283" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="C283" t="s">
-        <v>851</v>
+        <v>876</v>
       </c>
       <c r="D283" s="2">
         <v>11.532</v>
@@ -10546,13 +10735,13 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>852</v>
+        <v>877</v>
       </c>
       <c r="B284" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
       <c r="C284" t="s">
-        <v>854</v>
+        <v>879</v>
       </c>
       <c r="D284" s="2">
         <v>5.114</v>
@@ -10567,13 +10756,13 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="B285" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="C285" t="s">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="D285" s="2">
         <v>4.796</v>
@@ -10588,13 +10777,13 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="B286" t="s">
-        <v>859</v>
+        <v>884</v>
       </c>
       <c r="C286" t="s">
-        <v>860</v>
+        <v>885</v>
       </c>
       <c r="D286" s="2">
         <v>4.699</v>
@@ -10609,13 +10798,13 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>861</v>
+        <v>886</v>
       </c>
       <c r="B287" t="s">
-        <v>862</v>
+        <v>887</v>
       </c>
       <c r="C287" t="s">
-        <v>863</v>
+        <v>888</v>
       </c>
       <c r="D287" s="2">
         <v>4.192</v>
@@ -10630,13 +10819,13 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="B288" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="C288" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="D288" s="2">
         <v>4.738</v>
@@ -10651,13 +10840,13 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>867</v>
+        <v>892</v>
       </c>
       <c r="B289" t="s">
-        <v>868</v>
+        <v>893</v>
       </c>
       <c r="C289" t="s">
-        <v>869</v>
+        <v>894</v>
       </c>
       <c r="D289" s="2">
         <v>5.141</v>
@@ -10672,13 +10861,13 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="B290" t="s">
-        <v>871</v>
+        <v>896</v>
       </c>
       <c r="C290" t="s">
-        <v>872</v>
+        <v>897</v>
       </c>
       <c r="D290" s="2">
         <v>11.888</v>
@@ -10689,17 +10878,19 @@
       <c r="F290" s="2">
         <v>3.021</v>
       </c>
-      <c r="G290" s="3"/>
+      <c r="G290" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>873</v>
+        <v>898</v>
       </c>
       <c r="B291" t="s">
-        <v>874</v>
+        <v>899</v>
       </c>
       <c r="C291" t="s">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="D291" s="2">
         <v>35.382</v>
@@ -10710,17 +10901,19 @@
       <c r="F291" s="2">
         <v>8.979</v>
       </c>
-      <c r="G291" s="3"/>
+      <c r="G291" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>876</v>
+        <v>901</v>
       </c>
       <c r="B292" t="s">
-        <v>877</v>
+        <v>902</v>
       </c>
       <c r="C292" t="s">
-        <v>878</v>
+        <v>903</v>
       </c>
       <c r="D292" s="2">
         <v>4.209</v>
@@ -10735,13 +10928,13 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
       <c r="B293" t="s">
-        <v>880</v>
+        <v>905</v>
       </c>
       <c r="C293" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="D293" s="2">
         <v>5.177</v>
@@ -10756,34 +10949,34 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>882</v>
+        <v>907</v>
       </c>
       <c r="B294" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="C294" t="s">
-        <v>884</v>
+        <v>909</v>
       </c>
       <c r="D294" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E294" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F294" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G294" s="3"/>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>885</v>
+        <v>910</v>
       </c>
       <c r="B295" t="s">
-        <v>886</v>
+        <v>911</v>
       </c>
       <c r="C295" t="s">
-        <v>887</v>
+        <v>912</v>
       </c>
       <c r="D295" s="2">
         <v>3.635</v>
@@ -10798,13 +10991,13 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>888</v>
+        <v>913</v>
       </c>
       <c r="B296" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="C296" t="s">
-        <v>890</v>
+        <v>915</v>
       </c>
       <c r="D296" s="2">
         <v>25.529</v>
@@ -10815,38 +11008,40 @@
       <c r="F296" s="2">
         <v>7.581</v>
       </c>
-      <c r="G296" s="3"/>
+      <c r="G296" s="3" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="B297" t="s">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="C297" t="s">
-        <v>893</v>
+        <v>919</v>
       </c>
       <c r="D297" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E297" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F297" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G297" s="3"/>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>894</v>
+        <v>920</v>
       </c>
       <c r="B298" t="s">
-        <v>895</v>
+        <v>921</v>
       </c>
       <c r="C298" t="s">
-        <v>896</v>
+        <v>922</v>
       </c>
       <c r="D298" s="2">
         <v>25.529</v>
@@ -10857,17 +11052,19 @@
       <c r="F298" s="2">
         <v>7.581</v>
       </c>
-      <c r="G298" s="3"/>
+      <c r="G298" s="3" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="B299" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="C299" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="D299" s="2">
         <v>25.529</v>
@@ -10878,17 +11075,19 @@
       <c r="F299" s="2">
         <v>7.581</v>
       </c>
-      <c r="G299" s="3"/>
+      <c r="G299" s="3" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>900</v>
+        <v>928</v>
       </c>
       <c r="B300" t="s">
-        <v>901</v>
+        <v>929</v>
       </c>
       <c r="C300" t="s">
-        <v>902</v>
+        <v>930</v>
       </c>
       <c r="D300" s="2">
         <v>10.357</v>
@@ -10903,34 +11102,34 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>903</v>
+        <v>931</v>
       </c>
       <c r="B301" t="s">
-        <v>904</v>
+        <v>932</v>
       </c>
       <c r="C301" t="s">
-        <v>905</v>
+        <v>933</v>
       </c>
       <c r="D301" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E301" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F301" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G301" s="3"/>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>906</v>
+        <v>934</v>
       </c>
       <c r="B302" t="s">
-        <v>907</v>
+        <v>935</v>
       </c>
       <c r="C302" t="s">
-        <v>908</v>
+        <v>936</v>
       </c>
       <c r="D302" s="2">
         <v>3.598</v>
@@ -10945,13 +11144,13 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
       <c r="B303" t="s">
-        <v>910</v>
+        <v>938</v>
       </c>
       <c r="C303" t="s">
-        <v>911</v>
+        <v>939</v>
       </c>
       <c r="D303" s="2">
         <v>9.798</v>
@@ -10966,13 +11165,13 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>912</v>
+        <v>940</v>
       </c>
       <c r="B304" t="s">
-        <v>913</v>
+        <v>941</v>
       </c>
       <c r="C304" t="s">
-        <v>914</v>
+        <v>942</v>
       </c>
       <c r="D304" s="2">
         <v>44.164</v>
@@ -10983,38 +11182,40 @@
       <c r="F304" s="2">
         <v>11.056</v>
       </c>
-      <c r="G304" s="3"/>
+      <c r="G304" s="3" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>915</v>
+        <v>944</v>
       </c>
       <c r="B305" t="s">
-        <v>916</v>
+        <v>945</v>
       </c>
       <c r="C305" t="s">
-        <v>917</v>
+        <v>946</v>
       </c>
       <c r="D305" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E305" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F305" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G305" s="3"/>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>918</v>
+        <v>947</v>
       </c>
       <c r="B306" t="s">
-        <v>919</v>
+        <v>948</v>
       </c>
       <c r="C306" t="s">
-        <v>920</v>
+        <v>949</v>
       </c>
       <c r="D306" s="2">
         <v>3.715</v>
@@ -11029,13 +11230,13 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>921</v>
+        <v>950</v>
       </c>
       <c r="B307" t="s">
-        <v>922</v>
+        <v>951</v>
       </c>
       <c r="C307" t="s">
-        <v>923</v>
+        <v>952</v>
       </c>
       <c r="D307" s="2">
         <v>10.006</v>
@@ -11050,13 +11251,13 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>924</v>
+        <v>953</v>
       </c>
       <c r="B308" t="s">
-        <v>925</v>
+        <v>954</v>
       </c>
       <c r="C308" t="s">
-        <v>926</v>
+        <v>955</v>
       </c>
       <c r="D308" s="2">
         <v>3.333</v>
@@ -11071,13 +11272,13 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>927</v>
+        <v>956</v>
       </c>
       <c r="B309" t="s">
-        <v>928</v>
+        <v>957</v>
       </c>
       <c r="C309" t="s">
-        <v>929</v>
+        <v>958</v>
       </c>
       <c r="D309" s="2">
         <v>3.435</v>
@@ -11092,34 +11293,34 @@
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>930</v>
+        <v>959</v>
       </c>
       <c r="B310" t="s">
-        <v>931</v>
+        <v>960</v>
       </c>
       <c r="C310" t="s">
-        <v>932</v>
+        <v>961</v>
       </c>
       <c r="D310" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E310" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F310" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G310" s="3"/>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>933</v>
+        <v>962</v>
       </c>
       <c r="B311" t="s">
-        <v>934</v>
+        <v>963</v>
       </c>
       <c r="C311" t="s">
-        <v>935</v>
+        <v>964</v>
       </c>
       <c r="D311" s="2">
         <v>38.232</v>
@@ -11130,17 +11331,19 @@
       <c r="F311" s="2">
         <v>9.292</v>
       </c>
-      <c r="G311" s="3"/>
+      <c r="G311" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>936</v>
+        <v>965</v>
       </c>
       <c r="B312" t="s">
-        <v>937</v>
+        <v>966</v>
       </c>
       <c r="C312" t="s">
-        <v>938</v>
+        <v>967</v>
       </c>
       <c r="D312" s="2">
         <v>4.613</v>
@@ -11155,13 +11358,13 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>939</v>
+        <v>968</v>
       </c>
       <c r="B313" t="s">
-        <v>940</v>
+        <v>969</v>
       </c>
       <c r="C313" t="s">
-        <v>941</v>
+        <v>970</v>
       </c>
       <c r="D313" s="2">
         <v>9.975</v>
@@ -11176,13 +11379,13 @@
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>942</v>
+        <v>971</v>
       </c>
       <c r="B314" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="C314" t="s">
-        <v>944</v>
+        <v>973</v>
       </c>
       <c r="D314" s="2">
         <v>23.414</v>
@@ -11197,13 +11400,13 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>945</v>
+        <v>974</v>
       </c>
       <c r="B315" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="C315" t="s">
-        <v>947</v>
+        <v>976</v>
       </c>
       <c r="D315" s="2">
         <v>20.162</v>
@@ -11218,34 +11421,34 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>948</v>
+        <v>977</v>
       </c>
       <c r="B316" t="s">
-        <v>949</v>
+        <v>978</v>
       </c>
       <c r="C316" t="s">
-        <v>950</v>
+        <v>979</v>
       </c>
       <c r="D316" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E316" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F316" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G316" s="3"/>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>951</v>
+        <v>980</v>
       </c>
       <c r="B317" t="s">
-        <v>952</v>
+        <v>981</v>
       </c>
       <c r="C317" t="s">
-        <v>953</v>
+        <v>982</v>
       </c>
       <c r="D317" s="2">
         <v>26.34</v>
@@ -11260,13 +11463,13 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>954</v>
+        <v>983</v>
       </c>
       <c r="B318" t="s">
-        <v>955</v>
+        <v>984</v>
       </c>
       <c r="C318" t="s">
-        <v>956</v>
+        <v>985</v>
       </c>
       <c r="D318" s="2">
         <v>3.124</v>
@@ -11281,13 +11484,13 @@
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>957</v>
+        <v>986</v>
       </c>
       <c r="B319" t="s">
-        <v>958</v>
+        <v>987</v>
       </c>
       <c r="C319" t="s">
-        <v>959</v>
+        <v>988</v>
       </c>
       <c r="D319" s="2">
         <v>46.368</v>
@@ -11302,13 +11505,13 @@
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>960</v>
+        <v>989</v>
       </c>
       <c r="B320" t="s">
-        <v>961</v>
+        <v>990</v>
       </c>
       <c r="C320" t="s">
-        <v>962</v>
+        <v>991</v>
       </c>
       <c r="D320" s="2">
         <v>26.512</v>
@@ -11319,17 +11522,19 @@
       <c r="F320" s="2">
         <v>7.934</v>
       </c>
-      <c r="G320" s="3"/>
+      <c r="G320" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>963</v>
+        <v>992</v>
       </c>
       <c r="B321" t="s">
-        <v>964</v>
+        <v>993</v>
       </c>
       <c r="C321" t="s">
-        <v>965</v>
+        <v>994</v>
       </c>
       <c r="D321" s="2">
         <v>68.208</v>
@@ -11340,17 +11545,19 @@
       <c r="F321" s="2">
         <v>17.178</v>
       </c>
-      <c r="G321" s="3"/>
+      <c r="G321" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>966</v>
+        <v>995</v>
       </c>
       <c r="B322" t="s">
-        <v>967</v>
+        <v>996</v>
       </c>
       <c r="C322" t="s">
-        <v>968</v>
+        <v>997</v>
       </c>
       <c r="D322" s="2">
         <v>76.128</v>
@@ -11361,17 +11568,19 @@
       <c r="F322" s="2">
         <v>19.608</v>
       </c>
-      <c r="G322" s="3"/>
+      <c r="G322" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>969</v>
+        <v>998</v>
       </c>
       <c r="B323" t="s">
-        <v>970</v>
+        <v>999</v>
       </c>
       <c r="C323" t="s">
-        <v>971</v>
+        <v>1000</v>
       </c>
       <c r="D323" s="2">
         <v>30.138</v>
@@ -11382,17 +11591,19 @@
       <c r="F323" s="2">
         <v>7.401</v>
       </c>
-      <c r="G323" s="3"/>
+      <c r="G323" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>972</v>
+        <v>1001</v>
       </c>
       <c r="B324" t="s">
-        <v>973</v>
+        <v>1002</v>
       </c>
       <c r="C324" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="D324" s="2">
         <v>36.63</v>
@@ -11403,17 +11614,19 @@
       <c r="F324" s="2">
         <v>9.36</v>
       </c>
-      <c r="G324" s="3"/>
+      <c r="G324" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>975</v>
+        <v>1004</v>
       </c>
       <c r="B325" t="s">
-        <v>976</v>
+        <v>1005</v>
       </c>
       <c r="C325" t="s">
-        <v>977</v>
+        <v>1006</v>
       </c>
       <c r="D325" s="2">
         <v>32.664</v>
@@ -11428,13 +11641,13 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>978</v>
+        <v>1007</v>
       </c>
       <c r="B326" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="C326" t="s">
-        <v>980</v>
+        <v>1009</v>
       </c>
       <c r="D326" s="2">
         <v>67.854</v>
@@ -11445,17 +11658,19 @@
       <c r="F326" s="2">
         <v>19.659</v>
       </c>
-      <c r="G326" s="3"/>
+      <c r="G326" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>981</v>
+        <v>1010</v>
       </c>
       <c r="B327" t="s">
-        <v>982</v>
+        <v>1011</v>
       </c>
       <c r="C327" t="s">
-        <v>983</v>
+        <v>1012</v>
       </c>
       <c r="D327" s="2">
         <v>32.463</v>
@@ -11466,17 +11681,19 @@
       <c r="F327" s="2">
         <v>8.094</v>
       </c>
-      <c r="G327" s="3"/>
+      <c r="G327" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>984</v>
+        <v>1013</v>
       </c>
       <c r="B328" t="s">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="C328" t="s">
-        <v>986</v>
+        <v>1015</v>
       </c>
       <c r="D328" s="2">
         <v>33.228</v>
@@ -11487,17 +11704,19 @@
       <c r="F328" s="2">
         <v>8.325</v>
       </c>
-      <c r="G328" s="3"/>
+      <c r="G328" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>987</v>
+        <v>1016</v>
       </c>
       <c r="B329" t="s">
-        <v>988</v>
+        <v>1017</v>
       </c>
       <c r="C329" t="s">
-        <v>989</v>
+        <v>1018</v>
       </c>
       <c r="D329" s="2">
         <v>32.442</v>
@@ -11508,17 +11727,19 @@
       <c r="F329" s="2">
         <v>8.088</v>
       </c>
-      <c r="G329" s="3"/>
+      <c r="G329" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>990</v>
+        <v>1019</v>
       </c>
       <c r="B330" t="s">
-        <v>991</v>
+        <v>1020</v>
       </c>
       <c r="C330" t="s">
-        <v>992</v>
+        <v>1021</v>
       </c>
       <c r="D330" s="2">
         <v>37.119</v>
@@ -11529,17 +11750,19 @@
       <c r="F330" s="2">
         <v>9.51</v>
       </c>
-      <c r="G330" s="3"/>
+      <c r="G330" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>993</v>
+        <v>1022</v>
       </c>
       <c r="B331" t="s">
-        <v>994</v>
+        <v>1023</v>
       </c>
       <c r="C331" t="s">
-        <v>995</v>
+        <v>1024</v>
       </c>
       <c r="D331" s="2">
         <v>33</v>
@@ -11554,13 +11777,13 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>996</v>
+        <v>1025</v>
       </c>
       <c r="B332" t="s">
-        <v>997</v>
+        <v>1026</v>
       </c>
       <c r="C332" t="s">
-        <v>998</v>
+        <v>1027</v>
       </c>
       <c r="D332" s="2">
         <v>34.362</v>
@@ -11575,13 +11798,13 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>999</v>
+        <v>1028</v>
       </c>
       <c r="B333" t="s">
-        <v>1000</v>
+        <v>1029</v>
       </c>
       <c r="C333" t="s">
-        <v>1001</v>
+        <v>1030</v>
       </c>
       <c r="D333" s="2">
         <v>32.751</v>
@@ -11592,17 +11815,19 @@
       <c r="F333" s="2">
         <v>8.181</v>
       </c>
-      <c r="G333" s="3"/>
+      <c r="G333" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>1002</v>
+        <v>1031</v>
       </c>
       <c r="B334" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="C334" t="s">
-        <v>1004</v>
+        <v>1033</v>
       </c>
       <c r="D334" s="2">
         <v>72.558</v>
@@ -11613,17 +11838,19 @@
       <c r="F334" s="2">
         <v>18.504</v>
       </c>
-      <c r="G334" s="3"/>
+      <c r="G334" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>1005</v>
+        <v>1034</v>
       </c>
       <c r="B335" t="s">
-        <v>1006</v>
+        <v>1035</v>
       </c>
       <c r="C335" t="s">
-        <v>1007</v>
+        <v>1036</v>
       </c>
       <c r="D335" s="2">
         <v>87.039</v>
@@ -11634,17 +11861,19 @@
       <c r="F335" s="2">
         <v>26.532</v>
       </c>
-      <c r="G335" s="3"/>
+      <c r="G335" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
       <c r="B336" t="s">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="C336" t="s">
-        <v>1010</v>
+        <v>1039</v>
       </c>
       <c r="D336" s="2">
         <v>13.419</v>
@@ -11655,17 +11884,19 @@
       <c r="F336" s="2">
         <v>2.793</v>
       </c>
-      <c r="G336" s="3"/>
+      <c r="G336" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>1011</v>
+        <v>1040</v>
       </c>
       <c r="B337" t="s">
-        <v>1012</v>
+        <v>1041</v>
       </c>
       <c r="C337" t="s">
-        <v>1013</v>
+        <v>1042</v>
       </c>
       <c r="D337" s="2">
         <v>30.549</v>
@@ -11676,17 +11907,19 @@
       <c r="F337" s="2">
         <v>7.524</v>
       </c>
-      <c r="G337" s="3"/>
+      <c r="G337" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>1014</v>
+        <v>1043</v>
       </c>
       <c r="B338" t="s">
-        <v>1015</v>
+        <v>1044</v>
       </c>
       <c r="C338" t="s">
-        <v>1016</v>
+        <v>1045</v>
       </c>
       <c r="D338" s="2">
         <v>34.509</v>
@@ -11697,17 +11930,19 @@
       <c r="F338" s="2">
         <v>8.712</v>
       </c>
-      <c r="G338" s="3"/>
+      <c r="G338" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1017</v>
+        <v>1046</v>
       </c>
       <c r="B339" t="s">
-        <v>1018</v>
+        <v>1047</v>
       </c>
       <c r="C339" t="s">
-        <v>1019</v>
+        <v>1048</v>
       </c>
       <c r="D339" s="2">
         <v>35.982</v>
@@ -11722,13 +11957,13 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1020</v>
+        <v>1049</v>
       </c>
       <c r="B340" t="s">
-        <v>1021</v>
+        <v>1050</v>
       </c>
       <c r="C340" t="s">
-        <v>1022</v>
+        <v>1051</v>
       </c>
       <c r="D340" s="2">
         <v>22.913</v>
@@ -11739,59 +11974,63 @@
       <c r="F340" s="2">
         <v>6.656</v>
       </c>
-      <c r="G340" s="3"/>
+      <c r="G340" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1023</v>
+        <v>1052</v>
       </c>
       <c r="B341" t="s">
-        <v>1024</v>
+        <v>1053</v>
       </c>
       <c r="C341" t="s">
-        <v>1025</v>
+        <v>1054</v>
       </c>
       <c r="D341" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E341" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F341" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G341" s="3"/>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1026</v>
+        <v>1055</v>
       </c>
       <c r="B342" t="s">
-        <v>1027</v>
+        <v>1056</v>
       </c>
       <c r="C342" t="s">
-        <v>1028</v>
+        <v>1057</v>
       </c>
       <c r="D342" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E342" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F342" t="s">
-        <v>81</v>
-      </c>
-      <c r="G342" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G342" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1029</v>
+        <v>1058</v>
       </c>
       <c r="B343" t="s">
-        <v>1030</v>
+        <v>1059</v>
       </c>
       <c r="C343" t="s">
-        <v>1031</v>
+        <v>1060</v>
       </c>
       <c r="D343" s="2">
         <v>5.154</v>
@@ -11806,13 +12045,13 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="B344" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
       <c r="C344" t="s">
-        <v>1034</v>
+        <v>1063</v>
       </c>
       <c r="D344" s="2">
         <v>16.371</v>
@@ -11823,17 +12062,19 @@
       <c r="F344" s="2">
         <v>4.089</v>
       </c>
-      <c r="G344" s="3"/>
+      <c r="G344" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>1035</v>
+        <v>1064</v>
       </c>
       <c r="B345" t="s">
-        <v>1036</v>
+        <v>1065</v>
       </c>
       <c r="C345" t="s">
-        <v>1037</v>
+        <v>1066</v>
       </c>
       <c r="D345" s="2">
         <v>4.403</v>
@@ -11848,13 +12089,13 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>1038</v>
+        <v>1067</v>
       </c>
       <c r="B346" t="s">
-        <v>1039</v>
+        <v>1068</v>
       </c>
       <c r="C346" t="s">
-        <v>1040</v>
+        <v>1069</v>
       </c>
       <c r="D346" s="2">
         <v>3.712</v>
@@ -11869,13 +12110,13 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>1041</v>
+        <v>1070</v>
       </c>
       <c r="B347" t="s">
-        <v>1042</v>
+        <v>1071</v>
       </c>
       <c r="C347" t="s">
-        <v>1043</v>
+        <v>1072</v>
       </c>
       <c r="D347" s="2">
         <v>216.512</v>
@@ -11890,13 +12131,13 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>1044</v>
+        <v>1073</v>
       </c>
       <c r="B348" t="s">
-        <v>1045</v>
+        <v>1074</v>
       </c>
       <c r="C348" t="s">
-        <v>1046</v>
+        <v>1075</v>
       </c>
       <c r="D348" s="2">
         <v>3.46</v>
@@ -11911,13 +12152,13 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>1047</v>
+        <v>1076</v>
       </c>
       <c r="B349" t="s">
-        <v>1048</v>
+        <v>1077</v>
       </c>
       <c r="C349" t="s">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="D349" s="2">
         <v>18.192</v>
@@ -11928,17 +12169,19 @@
       <c r="F349" s="2">
         <v>3.8</v>
       </c>
-      <c r="G349" s="3"/>
+      <c r="G349" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>1050</v>
+        <v>1079</v>
       </c>
       <c r="B350" t="s">
-        <v>1051</v>
+        <v>1080</v>
       </c>
       <c r="C350" t="s">
-        <v>1052</v>
+        <v>1081</v>
       </c>
       <c r="D350" s="2">
         <v>25.707</v>
@@ -11949,17 +12192,19 @@
       <c r="F350" s="2">
         <v>6.452</v>
       </c>
-      <c r="G350" s="3"/>
+      <c r="G350" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="B351" t="s">
-        <v>1054</v>
+        <v>1083</v>
       </c>
       <c r="C351" t="s">
-        <v>1055</v>
+        <v>1084</v>
       </c>
       <c r="D351" s="2">
         <v>9.711</v>
@@ -11974,13 +12219,13 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>1056</v>
+        <v>1085</v>
       </c>
       <c r="B352" t="s">
-        <v>1057</v>
+        <v>1086</v>
       </c>
       <c r="C352" t="s">
-        <v>1058</v>
+        <v>1087</v>
       </c>
       <c r="D352" s="2">
         <v>9.003</v>
@@ -11991,17 +12236,19 @@
       <c r="F352" s="2">
         <v>2.262</v>
       </c>
-      <c r="G352" s="3"/>
+      <c r="G352" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>1059</v>
+        <v>1088</v>
       </c>
       <c r="B353" t="s">
-        <v>1060</v>
+        <v>1089</v>
       </c>
       <c r="C353" t="s">
-        <v>1061</v>
+        <v>1090</v>
       </c>
       <c r="D353" s="2">
         <v>22</v>
@@ -12016,13 +12263,13 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>1062</v>
+        <v>1091</v>
       </c>
       <c r="B354" t="s">
-        <v>1063</v>
+        <v>1092</v>
       </c>
       <c r="C354" t="s">
-        <v>1064</v>
+        <v>1093</v>
       </c>
       <c r="D354" s="2">
         <v>5.182</v>
@@ -12037,13 +12284,13 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1065</v>
+        <v>1094</v>
       </c>
       <c r="B355" t="s">
-        <v>1066</v>
+        <v>1095</v>
       </c>
       <c r="C355" t="s">
-        <v>1067</v>
+        <v>1096</v>
       </c>
       <c r="D355" s="2">
         <v>3.15</v>
@@ -12058,13 +12305,13 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>1068</v>
+        <v>1097</v>
       </c>
       <c r="B356" t="s">
-        <v>1069</v>
+        <v>1098</v>
       </c>
       <c r="C356" t="s">
-        <v>1070</v>
+        <v>1099</v>
       </c>
       <c r="D356" s="2">
         <v>255</v>
@@ -12079,55 +12326,55 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>1071</v>
+        <v>1100</v>
       </c>
       <c r="B357" t="s">
-        <v>1072</v>
+        <v>1101</v>
       </c>
       <c r="C357" t="s">
-        <v>1073</v>
+        <v>1102</v>
       </c>
       <c r="D357" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E357" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F357" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G357" s="3"/>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>1074</v>
+        <v>1103</v>
       </c>
       <c r="B358" t="s">
-        <v>1075</v>
+        <v>1104</v>
       </c>
       <c r="C358" t="s">
-        <v>1076</v>
+        <v>1105</v>
       </c>
       <c r="D358" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E358" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F358" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G358" s="3"/>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>1077</v>
+        <v>1106</v>
       </c>
       <c r="B359" t="s">
-        <v>1078</v>
+        <v>1107</v>
       </c>
       <c r="C359" t="s">
-        <v>1079</v>
+        <v>1108</v>
       </c>
       <c r="D359" s="2">
         <v>27.188</v>
@@ -12142,13 +12389,13 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>1080</v>
+        <v>1109</v>
       </c>
       <c r="B360" t="s">
-        <v>1081</v>
+        <v>1110</v>
       </c>
       <c r="C360" t="s">
-        <v>1082</v>
+        <v>1111</v>
       </c>
       <c r="D360" s="2">
         <v>14.918</v>
@@ -12163,13 +12410,13 @@
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>1083</v>
+        <v>1112</v>
       </c>
       <c r="B361" t="s">
-        <v>1084</v>
+        <v>1113</v>
       </c>
       <c r="C361" t="s">
-        <v>1085</v>
+        <v>1114</v>
       </c>
       <c r="D361" s="2">
         <v>12.555</v>
@@ -12184,13 +12431,13 @@
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>1086</v>
+        <v>1115</v>
       </c>
       <c r="B362" t="s">
-        <v>1087</v>
+        <v>1116</v>
       </c>
       <c r="C362" t="s">
-        <v>1088</v>
+        <v>1117</v>
       </c>
       <c r="D362" s="2">
         <v>13.428</v>
@@ -12205,13 +12452,13 @@
     </row>
     <row r="363" spans="1:7">
       <c r="A363" t="s">
-        <v>1089</v>
+        <v>1118</v>
       </c>
       <c r="B363" t="s">
-        <v>1090</v>
+        <v>1119</v>
       </c>
       <c r="C363" t="s">
-        <v>1091</v>
+        <v>1120</v>
       </c>
       <c r="D363" s="2">
         <v>8.992</v>
@@ -12222,17 +12469,19 @@
       <c r="F363" s="2">
         <v>2.289</v>
       </c>
-      <c r="G363" s="3"/>
+      <c r="G363" s="3" t="s">
+        <v>1121</v>
+      </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>1092</v>
+        <v>1122</v>
       </c>
       <c r="B364" t="s">
-        <v>1093</v>
+        <v>1123</v>
       </c>
       <c r="C364" t="s">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="D364" s="2">
         <v>7.597</v>
@@ -12247,13 +12496,13 @@
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="B365" t="s">
-        <v>1096</v>
+        <v>1126</v>
       </c>
       <c r="C365" t="s">
-        <v>1097</v>
+        <v>1127</v>
       </c>
       <c r="D365" s="2">
         <v>9.081</v>
@@ -12268,13 +12517,13 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>1098</v>
+        <v>1128</v>
       </c>
       <c r="B366" t="s">
-        <v>1099</v>
+        <v>1129</v>
       </c>
       <c r="C366" t="s">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="D366" s="2">
         <v>12.404</v>
@@ -12289,13 +12538,13 @@
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>1101</v>
+        <v>1131</v>
       </c>
       <c r="B367" t="s">
-        <v>1102</v>
+        <v>1132</v>
       </c>
       <c r="C367" t="s">
-        <v>1103</v>
+        <v>1133</v>
       </c>
       <c r="D367" s="2">
         <v>4.825</v>
@@ -12310,13 +12559,13 @@
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>1104</v>
+        <v>1134</v>
       </c>
       <c r="B368" t="s">
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="C368" t="s">
-        <v>1106</v>
+        <v>1136</v>
       </c>
       <c r="D368" s="2">
         <v>11.989</v>
@@ -12331,13 +12580,13 @@
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>1107</v>
+        <v>1137</v>
       </c>
       <c r="B369" t="s">
-        <v>1108</v>
+        <v>1138</v>
       </c>
       <c r="C369" t="s">
-        <v>1109</v>
+        <v>1139</v>
       </c>
       <c r="D369" s="2">
         <v>11.989</v>
@@ -12352,13 +12601,13 @@
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="B370" t="s">
-        <v>1111</v>
+        <v>1141</v>
       </c>
       <c r="C370" t="s">
-        <v>1112</v>
+        <v>1142</v>
       </c>
       <c r="D370" s="2">
         <v>11.989</v>
@@ -12373,13 +12622,13 @@
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1113</v>
+        <v>1143</v>
       </c>
       <c r="B371" t="s">
-        <v>1114</v>
+        <v>1144</v>
       </c>
       <c r="C371" t="s">
-        <v>1115</v>
+        <v>1145</v>
       </c>
       <c r="D371" s="2">
         <v>14.024</v>
@@ -12394,34 +12643,34 @@
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1116</v>
+        <v>1146</v>
       </c>
       <c r="B372" t="s">
-        <v>1117</v>
+        <v>1147</v>
       </c>
       <c r="C372" t="s">
-        <v>1118</v>
+        <v>1148</v>
       </c>
       <c r="D372" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E372" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F372" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G372" s="3"/>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1119</v>
+        <v>1149</v>
       </c>
       <c r="B373" t="s">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="C373" t="s">
-        <v>1121</v>
+        <v>1151</v>
       </c>
       <c r="D373" s="2">
         <v>3.586</v>
@@ -12436,13 +12685,13 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1122</v>
+        <v>1152</v>
       </c>
       <c r="B374" t="s">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="C374" t="s">
-        <v>1124</v>
+        <v>1154</v>
       </c>
       <c r="D374" s="2">
         <v>11.989</v>
@@ -12457,13 +12706,13 @@
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1125</v>
+        <v>1155</v>
       </c>
       <c r="B375" t="s">
-        <v>1126</v>
+        <v>1156</v>
       </c>
       <c r="C375" t="s">
-        <v>1127</v>
+        <v>1157</v>
       </c>
       <c r="D375" s="2">
         <v>6.28</v>
@@ -12478,13 +12727,13 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="B376" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
       <c r="C376" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
       <c r="D376" s="2">
         <v>11.989</v>
@@ -12499,13 +12748,13 @@
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
       <c r="B377" t="s">
-        <v>1132</v>
+        <v>1162</v>
       </c>
       <c r="C377" t="s">
-        <v>1133</v>
+        <v>1163</v>
       </c>
       <c r="D377" s="2">
         <v>80.189</v>
@@ -12520,13 +12769,13 @@
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1134</v>
+        <v>1164</v>
       </c>
       <c r="B378" t="s">
-        <v>1135</v>
+        <v>1165</v>
       </c>
       <c r="C378" t="s">
-        <v>1136</v>
+        <v>1166</v>
       </c>
       <c r="D378" s="2">
         <v>34.981</v>
@@ -12537,17 +12786,19 @@
       <c r="F378" s="2">
         <v>11.661</v>
       </c>
-      <c r="G378" s="3"/>
+      <c r="G378" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1137</v>
+        <v>1167</v>
       </c>
       <c r="B379" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="C379" t="s">
-        <v>1139</v>
+        <v>1169</v>
       </c>
       <c r="D379" s="2">
         <v>22.127</v>
@@ -12562,13 +12813,13 @@
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="B380" t="s">
-        <v>1141</v>
+        <v>1171</v>
       </c>
       <c r="C380" t="s">
-        <v>1142</v>
+        <v>1172</v>
       </c>
       <c r="D380" s="2">
         <v>25.529</v>
@@ -12579,38 +12830,42 @@
       <c r="F380" s="2">
         <v>7.581</v>
       </c>
-      <c r="G380" s="3"/>
+      <c r="G380" s="3" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="B381" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="C381" t="s">
-        <v>1145</v>
+        <v>1176</v>
       </c>
       <c r="D381" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E381" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F381" t="s">
-        <v>81</v>
-      </c>
-      <c r="G381" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="G381" s="3" t="s">
+        <v>1177</v>
+      </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1146</v>
+        <v>1178</v>
       </c>
       <c r="B382" t="s">
-        <v>1147</v>
+        <v>1179</v>
       </c>
       <c r="C382" t="s">
-        <v>1148</v>
+        <v>1180</v>
       </c>
       <c r="D382" s="2">
         <v>25.529</v>
@@ -12621,17 +12876,19 @@
       <c r="F382" s="2">
         <v>7.581</v>
       </c>
-      <c r="G382" s="3"/>
+      <c r="G382" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1149</v>
+        <v>1181</v>
       </c>
       <c r="B383" t="s">
-        <v>1150</v>
+        <v>1182</v>
       </c>
       <c r="C383" t="s">
-        <v>1151</v>
+        <v>1183</v>
       </c>
       <c r="D383" s="2">
         <v>17.54</v>
@@ -12646,13 +12903,13 @@
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1152</v>
+        <v>1184</v>
       </c>
       <c r="B384" t="s">
-        <v>1153</v>
+        <v>1185</v>
       </c>
       <c r="C384" t="s">
-        <v>1154</v>
+        <v>1186</v>
       </c>
       <c r="D384" s="2">
         <v>11.48</v>
@@ -12663,59 +12920,61 @@
       <c r="F384" s="2">
         <v>2.897</v>
       </c>
-      <c r="G384" s="3"/>
+      <c r="G384" s="3" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1155</v>
+        <v>1187</v>
       </c>
       <c r="B385" t="s">
-        <v>1156</v>
+        <v>1188</v>
       </c>
       <c r="C385" t="s">
-        <v>1157</v>
+        <v>1189</v>
       </c>
       <c r="D385" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E385" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F385" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G385" s="3"/>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>1158</v>
+        <v>1190</v>
       </c>
       <c r="B386" t="s">
-        <v>1159</v>
+        <v>1191</v>
       </c>
       <c r="C386" t="s">
-        <v>1160</v>
+        <v>1192</v>
       </c>
       <c r="D386" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E386" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F386" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G386" s="3"/>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>1161</v>
+        <v>1193</v>
       </c>
       <c r="B387" t="s">
-        <v>1162</v>
+        <v>1194</v>
       </c>
       <c r="C387" t="s">
-        <v>1163</v>
+        <v>1195</v>
       </c>
       <c r="D387" s="2">
         <v>12.958</v>
@@ -12726,38 +12985,40 @@
       <c r="F387" s="2">
         <v>3.351</v>
       </c>
-      <c r="G387" s="3"/>
+      <c r="G387" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>1164</v>
+        <v>1196</v>
       </c>
       <c r="B388" t="s">
-        <v>1165</v>
+        <v>1197</v>
       </c>
       <c r="C388" t="s">
-        <v>1166</v>
+        <v>1198</v>
       </c>
       <c r="D388" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E388" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F388" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G388" s="3"/>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>1167</v>
+        <v>1199</v>
       </c>
       <c r="B389" t="s">
-        <v>1168</v>
+        <v>1200</v>
       </c>
       <c r="C389" t="s">
-        <v>1169</v>
+        <v>1201</v>
       </c>
       <c r="D389" s="2">
         <v>13.125</v>
@@ -12768,17 +13029,19 @@
       <c r="F389" s="2">
         <v>3.404</v>
       </c>
-      <c r="G389" s="3"/>
+      <c r="G389" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>1170</v>
+        <v>1202</v>
       </c>
       <c r="B390" t="s">
-        <v>1171</v>
+        <v>1203</v>
       </c>
       <c r="C390" t="s">
-        <v>1172</v>
+        <v>1204</v>
       </c>
       <c r="D390" s="2">
         <v>13.115</v>
@@ -12789,101 +13052,103 @@
       <c r="F390" s="2">
         <v>3.4</v>
       </c>
-      <c r="G390" s="3"/>
+      <c r="G390" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>1173</v>
+        <v>1205</v>
       </c>
       <c r="B391" t="s">
-        <v>1174</v>
+        <v>1206</v>
       </c>
       <c r="C391" t="s">
-        <v>1175</v>
+        <v>1207</v>
       </c>
       <c r="D391" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E391" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F391" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G391" s="3"/>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" t="s">
-        <v>1176</v>
+        <v>1208</v>
       </c>
       <c r="B392" t="s">
-        <v>1177</v>
+        <v>1209</v>
       </c>
       <c r="C392" t="s">
-        <v>1178</v>
+        <v>1210</v>
       </c>
       <c r="D392" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E392" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F392" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G392" s="3"/>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>1179</v>
+        <v>1211</v>
       </c>
       <c r="B393" t="s">
-        <v>1180</v>
+        <v>1212</v>
       </c>
       <c r="C393" t="s">
-        <v>1181</v>
+        <v>1213</v>
       </c>
       <c r="D393" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E393" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F393" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G393" s="3"/>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>1182</v>
+        <v>1214</v>
       </c>
       <c r="B394" t="s">
-        <v>1183</v>
+        <v>1215</v>
       </c>
       <c r="C394" t="s">
-        <v>1184</v>
+        <v>1216</v>
       </c>
       <c r="D394" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E394" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F394" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G394" s="3"/>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" t="s">
-        <v>1185</v>
+        <v>1217</v>
       </c>
       <c r="B395" t="s">
-        <v>1186</v>
+        <v>1218</v>
       </c>
       <c r="C395" t="s">
-        <v>1187</v>
+        <v>1219</v>
       </c>
       <c r="D395" s="2">
         <v>10.474</v>
@@ -12894,7 +13159,14 @@
       <c r="F395" s="2">
         <v>2.594</v>
       </c>
-      <c r="G395" s="3"/>
+      <c r="G395" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="G396" t="s">
+        <v>1220</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G395" etc:filterBottomFollowUsedRange="0">
